--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Rohit Kumar Raut</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9821137517</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9821137517</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -940,10 +938,8 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -954,7 +950,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,23 +483,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,19 +517,19 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -976,6 +976,217 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 9:15 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352600</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Dhanishwar Subedi</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Dhanishwar Subedi</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9851159410</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:15:18 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9851159410</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:00:32 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:15:18 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.68338</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Open Korean Bhasa - Language school Bhaktapur 44800, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>dhsubedi03@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>07:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.30336</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -990,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -998,12 +1209,12 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1027,7 +1238,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1037,7 +1248,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1048,7 +1259,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1271,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1283,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
@@ -1109,151 +1320,259 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352600</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Dhanishwar Subedi</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:15:18 AM</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:00:32 PM</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:15:18 AM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1046,10 +1046,8 @@
           <t>Dhanishwar Subedi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9851159410</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9851159410</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1084,10 +1082,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.68338</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.68338</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1143,25 +1139,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.30336</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.30336</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1210,7 +1202,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1542,7 +1534,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1179,6 +1179,213 @@
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 9:37 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352510</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9841255601</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:37:33 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841255601</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:05:06 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:37:33 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Lazimpat, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh@gamil.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Bishwojeet Adhikari</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB328</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 32m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1230,7 +1437,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1251,7 +1458,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1541,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
@@ -1411,7 +1618,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1426,143 +1633,166 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TKT1352600</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Dhanishwar Subedi</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>20h 14m</t>
         </is>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1239,20 +1239,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Rajesh Barjachrya</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9841255601</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9841255601</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1287,10 +1281,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1342,50 +1334,257 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB328</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 32m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352535</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Tuladhar</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Tuladhar</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9860088963</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01:43 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849694056</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20:00 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01:43 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Bungmati, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>07:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L9-CDB4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>21h 32m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 41m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1409,7 +1608,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1437,7 +1636,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1447,7 +1646,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1458,7 +1657,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1681,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 14m</t>
+          <t>20h 58m</t>
         </is>
       </c>
     </row>
@@ -1523,10 +1722,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1599,10 +1798,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -1795,6 +1994,73 @@
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>20h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352535</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Tuladhar</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01:43 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20:00 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01:43 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>21h 41m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1444,10 +1444,8 @@
           <t>Bijay Tuladhar</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9860088963</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9860088963</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1482,10 +1480,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1541,25 +1537,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L9-CDB4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1608,7 +1600,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2030,7 +2022,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1580,6 +1580,109 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:39 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1591,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1628,7 +1731,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1649,7 +1752,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -1743,84 +1846,75 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1926,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1847,210 +1941,248 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TKT1352600</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Dhanishwar Subedi</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>20h 14m</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TKT1352535</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Bijay Tuladhar</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>21h 41m</t>
         </is>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -513,12 +513,12 @@
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1683,6 +1683,1037 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352969</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9842295764</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:11:10 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9823137550</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:49:39 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:27:22 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.67706</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor,Shatya Sai baba Marg,House nu -46,Near Suprim Overseas Pvt Ltd,and Khaja Ghar, At Bindabas</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>acnares2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.3458</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>18h 16m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>18h 37m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>iptv related issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352779</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860469366</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860469366</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:48 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.7532644899109, 85.34095673714198 GPS Coordinates Nearest: KAT028-01-3/5-L26 (191m Road) Map: CG D</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9860469366@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>06:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L26-5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:19 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>iptv related issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352779</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9860469366</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860469366</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:48 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>27.7532644899109, 85.34095673714198 GPS Coordinates Nearest: KAT028-01-3/5-L26 (191m Road) Map: CG D</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9860469366@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>06:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L26-5</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:25:27 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:25:27 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>9d 21h 18m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>interent not working</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9865995180</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>LTP9700022257</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>27.646537000000006, 85.31367780674677, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>dexnineco@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>05:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>8d 21h 31m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1694,16 +2725,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1731,7 +2762,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1741,7 +2772,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1752,7 +2783,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1776,7 +2807,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 58m</t>
+          <t>2d 11h 22m</t>
         </is>
       </c>
     </row>
@@ -1817,14 +2848,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1847,344 +2878,627 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB box Damage Issue</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>TKT1352600</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Dhanishwar Subedi</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>20h 14m</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>TKT1352535</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Bijay Tuladhar</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>21h 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352779</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:48 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352779</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:48 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>8d 21h 31m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1750,10 +1750,8 @@
           <t>Naresh Acharya</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9842295764</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9842295764</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1788,10 +1786,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.67706</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.67706</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1843,25 +1839,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.3458</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.3458</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -1957,10 +1949,8 @@
           <t>Narayan kumar khatri</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860469366</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860469366</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2050,10 +2040,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2064,7 +2052,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2160,10 +2148,8 @@
           <t>Narayan kumar khatri</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9860469366</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9860469366</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2253,10 +2239,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2251,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2363,10 +2347,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2401,10 +2383,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.6907</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.6907</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2456,25 +2436,21 @@
           <t>Rahul Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2570,10 +2546,8 @@
           <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9865995180</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9865995180</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2608,10 +2582,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2667,25 +2639,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>CDB517</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2734,7 +2702,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3334,7 +3302,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -3401,7 +3369,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -3468,7 +3436,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2682,6 +2682,217 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353606</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9861804477</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04:05 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>LTP9861804477</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:54:48 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04:05 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.666100</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Nhu Pukhu (Rani Pokhari) Marg, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>02:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB105</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.322084</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 9m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2693,7 +2904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2702,7 +2913,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2730,7 +2941,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2740,7 +2951,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2751,7 +2962,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2986,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 11h 22m</t>
+          <t>2d 1h 50m</t>
         </is>
       </c>
     </row>
@@ -2816,14 +3027,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2942,14 +3153,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -3470,6 +3681,73 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353606</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04:05 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:54:48 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04:05 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2h 9m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -2749,10 +2749,8 @@
           <t>Sudip Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9861804477</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9861804477</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2787,10 +2785,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.666100</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.6661</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2846,50 +2842,874 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB105</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.322084</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.322084</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 9m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352339</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Shali Ghimire</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Shali Ghimire</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9851159666</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19:17 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9851159666</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:30:19 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19:17 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.7307</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Devkota Brothers, P8J9+35H, Samakhushi - Ranibari Rd, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>ghimire_ks@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>11:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Anu Bogati</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L16-7</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.3175</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>2h 9m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 48m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>slow Internet</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348195</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26:25 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 11:21:12 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26:25 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Clicked Location 27.70858, 85.33194 Nearest: CDB436 (45m Road) Map: CG Putalisadak, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>08:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB256</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 5m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352921</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.727574</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Corona school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB264</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.291697</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352921</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.727574</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Corona school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB264</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.291697</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2904,12 +3724,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -2941,7 +3761,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2951,7 +3771,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2962,7 +3782,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2974,7 +3794,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 59m</t>
         </is>
       </c>
     </row>
@@ -2986,7 +3806,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 50m</t>
+          <t>1d 22h 11m</t>
         </is>
       </c>
     </row>
@@ -3027,14 +3847,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -3081,14 +3901,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3153,14 +3973,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -3241,187 +4061,143 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1352600</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Dhanishwar Subedi</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>30 Sep 2026 01:00:32 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1352535</t>
+          <t>TKT1352600</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bijay Tuladhar</t>
+          <t>Dhanishwar Subedi</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3451,22 +4227,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:20:00 PM</t>
+          <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3476,29 +4252,29 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>21h 41m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1352779</t>
+          <t>TKT1352535</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Narayan kumar khatri</t>
+          <t>Bijay Tuladhar</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3518,22 +4294,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:58:48 PM</t>
+          <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3543,7 +4319,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>21h 41m</t>
         </is>
       </c>
     </row>
@@ -3585,7 +4361,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -3617,22 +4393,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1342441</t>
+          <t>TKT1352779</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Dex Nine pvt. Ltd.</t>
+          <t>Narayan kumar khatri</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3652,22 +4428,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 01:33:16 PM</t>
+          <t>30 Sep 2026 02:58:48 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -3677,74 +4453,409 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>8d 21h 31m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>8d 21h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>TKT1353606</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Sudip Shrestha</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:54:48 AM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>2h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352339</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Shali Ghimire</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19:17 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:30:19 AM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19:17 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1348195</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26:25 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 11:21:12 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26:25 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>4d 1h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352921</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352921</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2952,10 +2952,8 @@
           <t>Kamal Shali Ghimire</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9851159666</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9851159666</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -2990,10 +2988,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.7307</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.7307</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3049,25 +3045,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L16-7</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.3175</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.3175</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3163,10 +3155,8 @@
           <t>Anuj  Kuwar</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9860614634</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9860614634</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3234,10 +3224,8 @@
           <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
-      <c r="AH14" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH14" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
@@ -3256,10 +3244,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3270,7 +3256,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3366,10 +3352,8 @@
           <t>Suresh Babu Amgain</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9851067572</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9851067572</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3404,10 +3388,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.727574</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.727574</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3459,25 +3441,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB264</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.291697</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.291697</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3573,10 +3551,8 @@
           <t>Suresh Babu Amgain</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851067572</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851067572</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3611,10 +3587,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.727574</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.727574</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3666,25 +3640,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>CDB264</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.291697</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.291697</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3733,7 +3703,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4624,7 +4594,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4691,7 +4661,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4758,7 +4728,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -4825,7 +4795,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3683,6 +3683,416 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351456</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Puja Regmi</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Puja Regmi</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9843038600</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49:05 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9843038600</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:48:59 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49:05 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Swimming Pool Marg Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>19:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:02 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352734</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Subedi</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Subedi</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9851175712</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9851175712</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:34:05 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.756192</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Q822+54F way Tarakeshwar 44600,Near Sunflower Academy (English Medium SS) , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>subedirupak8@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>08:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L5-1</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.29951</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3694,7 +4104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3703,7 +4113,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3731,7 +4141,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +4151,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -3752,7 +4162,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -3764,7 +4174,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 59m</t>
+          <t>3h 19m</t>
         </is>
       </c>
     </row>
@@ -3776,7 +4186,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 11m</t>
+          <t>1d 20h 16m</t>
         </is>
       </c>
     </row>
@@ -3817,14 +4227,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -3943,14 +4353,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -4829,6 +5239,140 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351456</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Puja Regmi</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49:05 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:48:59 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49:05 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352734</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Rupak Subedi</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:34:05 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -3750,10 +3750,8 @@
           <t>Puja Regmi</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9843038600</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9843038600</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3839,10 +3837,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3853,7 +3849,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3949,10 +3945,8 @@
           <t>Rupak Subedi</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9851175712</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9851175712</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3987,10 +3981,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.756192</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.756192</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4046,50 +4038,464 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L5-1</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.29951</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.29951</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:03 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>router uprade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353630</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana Yadav</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana Yadav</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9819622436</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:03:40 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9844495200</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:10:10 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:03:40 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.656123</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Mahalaxmi municipality baghmati Nepal , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>yadavranjana099@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB025</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.339142</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>22h 28m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2h 53m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352510</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9841255601</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:08:32 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841255601</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:05:06 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:08:32 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Lazimpat, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh@gamil.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>11:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bishwojeet Adhikari</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB328</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -4104,12 +4510,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -4141,7 +4547,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -4151,7 +4557,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -4162,7 +4568,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4580,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 19m</t>
+          <t>3h 4m</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4592,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 16m</t>
+          <t>1d 18h 48m</t>
         </is>
       </c>
     </row>
@@ -4227,14 +4633,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -4245,14 +4651,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -4353,14 +4759,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -4376,14 +4782,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5678,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5339,14 +5745,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 01:02:33 PM</t>
@@ -5370,6 +5776,73 @@
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>22h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352510</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:08:32 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:05:06 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:08:32 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 3m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4148,10 +4148,8 @@
           <t>Ranjana Yadav</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9819622436</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9819622436</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4186,10 +4184,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.656123</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.656123</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4241,25 +4237,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB025</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.339142</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.339142</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4345,20 +4337,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Rajesh Barjachrya</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9841255601</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9841255601</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4393,10 +4379,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4452,50 +4436,257 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>CDB328</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352942</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9803282720</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:27:30 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9803282720</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:37:44 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:27:30 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>BhaktapurKaushaltaarTersetaar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>dunish550@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>06:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 3m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>20h 49m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4547,7 +4738,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -4557,7 +4748,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -4568,7 +4759,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4771,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 4m</t>
+          <t>2h 51m</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4783,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 48m</t>
+          <t>1d 17h 14m</t>
         </is>
       </c>
     </row>
@@ -4687,14 +4878,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4870,187 +5061,143 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1352600</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Dhanishwar Subedi</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>30 Sep 2026 01:00:32 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>20h 14m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1352535</t>
+          <t>TKT1352600</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Bijay Tuladhar</t>
+          <t>Dhanishwar Subedi</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5080,22 +5227,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:20:00 PM</t>
+          <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5105,29 +5252,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>21h 41m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1352779</t>
+          <t>TKT1352535</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Narayan kumar khatri</t>
+          <t>Bijay Tuladhar</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5147,22 +5294,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:58:48 PM</t>
+          <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5172,7 +5319,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>21h 41m</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5361,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -5246,22 +5393,22 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1342441</t>
+          <t>TKT1352779</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Dex Nine pvt. Ltd.</t>
+          <t>Narayan kumar khatri</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5281,22 +5428,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 01:33:16 PM</t>
+          <t>30 Sep 2026 02:58:48 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5306,19 +5453,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>8d 21h 31m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1353606</t>
+          <t>TKT1342441</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -5348,22 +5495,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:54:48 AM</t>
+          <t>22 Sep 2026 01:33:16 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5373,19 +5520,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2h 9m</t>
+          <t>8d 21h 31m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1352339</t>
+          <t>TKT1353606</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Kamal Shali Ghimire</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5415,22 +5562,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 10:30:19 AM</t>
+          <t>01 Oct 2026 09:54:48 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5440,29 +5587,29 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 48m</t>
+          <t>2h 9m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1348195</t>
+          <t>TKT1352339</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Anuj  Kuwar</t>
+          <t>Kamal Shali Ghimire</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -5482,22 +5629,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 11:21:12 AM</t>
+          <t>30 Sep 2026 10:30:19 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -5507,39 +5654,39 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>4d 1h 5m</t>
+          <t>1d 1h 48m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1352921</t>
+          <t>TKT1348195</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Suresh Babu Amgain</t>
+          <t>Anuj  Kuwar</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -5549,32 +5696,32 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>27 Sep 2026 11:21:12 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:28:17 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>4d 1h 5m</t>
         </is>
       </c>
     </row>
@@ -5648,12 +5795,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1351456</t>
+          <t>TKT1352921</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Puja Regmi</t>
+          <t>Suresh Babu Amgain</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -5668,12 +5815,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5683,44 +5830,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:48:59 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>01 Oct 2026 12:28:17 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 58m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 23h</t>
+          <t>19h 58m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1352734</t>
+          <t>TKT1351456</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Rupak Subedi</t>
+          <t>Puja Regmi</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -5750,22 +5897,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:34:05 PM</t>
+          <t>29 Sep 2026 01:48:59 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -5775,74 +5922,208 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>1d 23h</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>TKT1352734</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Subedi</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:34:05 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>TKT1352510</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Rajesh Barjachrya</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>30 Sep 2026 12:05:06 PM</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>1d 1h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352942</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:27:30 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:37:44 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:27:30 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>20h 49m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4546,10 +4546,8 @@
           <t>Unish Dulal</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9803282720</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9803282720</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4584,10 +4582,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4643,25 +4639,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4710,7 +4702,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6093,7 +6085,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4682,6 +4682,1244 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353222</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Mohit Shrestha</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Mohit Shrestha</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9813626257</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:48:59 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9813626257</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:48:59 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:57:46 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.71686</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>P883+P4V Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>04:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB478</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.3028</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>18h 8m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>18h 8m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:55 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353527</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Elina Maharjan</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Elina Maharjan</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9802206622</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:55:44 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9802206622</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 08:59:56 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:55:44 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.68315</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Kupondole Hotel Kutumba, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>maharjanelina05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.31638</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>4h 55m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353546</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>som Bahadur thing</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>som Bahadur thing</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851211866</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851211866</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:21:53 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Prime Colony Society - Housing society M8H3+8J9 Naya Bato Lalitpur 44600, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>9851211866@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>03:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>4h 28m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344890</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Timilsina</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Timilsina</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851326768</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 08:51:26 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9866486431</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 02:16:43 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:03:01 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.679234</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Near Chokha Binayak Sthan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>timilsinakrish@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L16-1</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.444639</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>17h 11m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>6d 23h 46m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:01 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353055</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9708478044</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:41 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9849426510</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:41 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:01:11 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.682799</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Holy garden school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L38-7</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.389388</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>20h 28m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>20h 28m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:58 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352969</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9842295764</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:58:17 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9823137550</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:49:39 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:58:17 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.67706</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor,Shatya Sai baba Marg,House nu -46,Near Suprim Overseas Pvt Ltd,and Khaja Ghar, At Bindabas</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>acnares2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>07:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.3458</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 8m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4693,7 +5931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4702,7 +5940,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4730,7 +5968,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -4740,7 +5978,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4751,7 +5989,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -4763,7 +6001,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 51m</t>
+          <t>3h 25m</t>
         </is>
       </c>
     </row>
@@ -4775,7 +6013,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 14m</t>
+          <t>1d 12h 31m</t>
         </is>
       </c>
     </row>
@@ -4816,14 +6054,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -4870,14 +6108,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -4942,14 +6180,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -5080,14 +6318,14 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6119,6 +7357,207 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353222</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Mohit Shrestha</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:48:59 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:48:59 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:57:46 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>18h 8m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>18h 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353546</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>som Bahadur thing</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:21:53 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>4h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352969</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:58:17 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:49:39 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:58:17 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>21h 8m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4749,10 +4749,8 @@
           <t>Mohit Shrestha</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9813626257</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9813626257</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4787,10 +4785,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.71686</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.71686</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4842,25 +4838,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB478</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.3028</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.3028</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4956,10 +4948,8 @@
           <t>Elina Maharjan</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9802206622</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9802206622</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4994,10 +4984,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.68315</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.68315</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5049,25 +5037,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.31638</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.31638</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5163,10 +5147,8 @@
           <t>som Bahadur thing</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851211866</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851211866</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5256,10 +5238,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -5270,7 +5250,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5366,10 +5346,8 @@
           <t>Bijay Timilsina</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851326768</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851326768</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5404,10 +5382,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.679234</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.679234</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5459,25 +5435,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>L16-1</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.444639</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.444639</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5573,10 +5545,8 @@
           <t>BISHNU HARI SHRESTHA</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9708478044</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9708478044</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5611,10 +5581,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.682799</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.682799</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5662,25 +5630,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L38-7</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.389388</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.389388</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5776,10 +5740,8 @@
           <t>Naresh Acharya</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9842295764</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9842295764</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5814,10 +5776,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.67706</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.67706</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5873,50 +5833,253 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.3458</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.3458</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 8m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
           <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>21h 8m</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353054</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakur</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakur</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9805889944</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 08:41:08 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>BKT9805889944</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:23 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:07:15 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.659463</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Changathali, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Naman Mallik</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.359684</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>5h 26m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 34m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -5940,7 +6103,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5968,7 +6131,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -5989,7 +6152,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -6072,14 +6235,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -6203,14 +6366,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7553,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -7457,7 +7620,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -7524,7 +7687,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW28"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -5933,20 +5933,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Umesh Thakur</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9805889944</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9805889944</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5981,10 +5975,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.659463</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.659463</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -6036,48 +6028,864 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.359684</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.359684</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>5h 26m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 34m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>5h 26m</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>20h 34m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353804</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:46:37 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:46:37 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:29:08 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>balkot, shanti chock, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L53-8</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV28" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW28" s="3" t="inlineStr">
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:24 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344823</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Man Shrestha</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Man Shrestha</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9843807409</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:24:28 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9849669368</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:20:51 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:24:28 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.67556</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Khachhen, 16, Shakyai Unique emporium nearby, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>sarojmansh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>13:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.32319</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>7d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353539</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Chakra prasad thapa magar</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Chakra prasad thapa magar</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9821507017</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9851122942</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:13:51 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Near Lumbini Gas, P8P7+G4P, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>sajinthapa98@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>04:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L46-5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>5h 13m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:22 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352583</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:15:03 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:49:09 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:22:49 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>11:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>23h 7m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 33m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
         </is>
@@ -6094,16 +6902,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6131,7 +6939,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -6141,7 +6949,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6152,7 +6960,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6972,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 25m</t>
+          <t>4h 3m</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6984,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 31m</t>
+          <t>1d 17h 2m</t>
         </is>
       </c>
     </row>
@@ -6217,14 +7025,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -6253,10 +7061,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -6343,14 +7151,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +7234,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -6454,7 +7262,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -6477,187 +7285,143 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1352600</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Dhanishwar Subedi</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>30 Sep 2026 01:00:32 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>20h 14m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1352535</t>
+          <t>TKT1352600</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bijay Tuladhar</t>
+          <t>Dhanishwar Subedi</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6687,22 +7451,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:20:00 PM</t>
+          <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -6712,29 +7476,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>21h 41m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1352779</t>
+          <t>TKT1352535</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Narayan kumar khatri</t>
+          <t>Bijay Tuladhar</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -6754,22 +7518,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:58:48 PM</t>
+          <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -6779,7 +7543,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>21h 41m</t>
         </is>
       </c>
     </row>
@@ -6821,7 +7585,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -6853,22 +7617,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1342441</t>
+          <t>TKT1352779</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Dex Nine pvt. Ltd.</t>
+          <t>Narayan kumar khatri</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6888,22 +7652,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 01:33:16 PM</t>
+          <t>30 Sep 2026 02:58:48 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -6913,19 +7677,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>8d 21h 31m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1353606</t>
+          <t>TKT1342441</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6955,22 +7719,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:54:48 AM</t>
+          <t>22 Sep 2026 01:33:16 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -6980,19 +7744,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2h 9m</t>
+          <t>8d 21h 31m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1352339</t>
+          <t>TKT1353606</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Kamal Shali Ghimire</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7022,22 +7786,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 10:30:19 AM</t>
+          <t>01 Oct 2026 09:54:48 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7047,29 +7811,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 48m</t>
+          <t>2h 9m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1348195</t>
+          <t>TKT1352339</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Anuj  Kuwar</t>
+          <t>Kamal Shali Ghimire</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -7089,22 +7853,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 11:21:12 AM</t>
+          <t>30 Sep 2026 10:30:19 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -7114,39 +7878,39 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 5m</t>
+          <t>1d 1h 48m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1352921</t>
+          <t>TKT1348195</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Suresh Babu Amgain</t>
+          <t>Anuj  Kuwar</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -7156,32 +7920,32 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>27 Sep 2026 11:21:12 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:28:17 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>4d 1h 5m</t>
         </is>
       </c>
     </row>
@@ -7255,12 +8019,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1351456</t>
+          <t>TKT1352921</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Puja Regmi</t>
+          <t>Suresh Babu Amgain</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7275,12 +8039,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -7290,44 +8054,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:48:59 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>01 Oct 2026 12:28:17 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 58m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 23h</t>
+          <t>19h 58m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1352734</t>
+          <t>TKT1351456</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Rupak Subedi</t>
+          <t>Puja Regmi</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7357,22 +8121,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:34:05 PM</t>
+          <t>29 Sep 2026 01:48:59 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7382,29 +8146,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>1d 23h</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1352510</t>
+          <t>TKT1352734</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Rajesh Barjachrya</t>
+          <t>Rupak Subedi</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7424,22 +8188,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:05:06 PM</t>
+          <t>30 Sep 2026 02:34:05 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -7449,29 +8213,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 3m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1352942</t>
+          <t>TKT1352510</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Rajesh Barjachrya</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -7491,22 +8255,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:37:44 PM</t>
+          <t>30 Sep 2026 12:05:06 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -7516,39 +8280,39 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>20h 49m</t>
+          <t>1d 1h 3m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1353222</t>
+          <t>TKT1352942</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Mohit Shrestha</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -7558,44 +8322,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>30 Sep 2026 04:37:44 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:57:46 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>20h 49m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1353546</t>
+          <t>TKT1353222</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>som Bahadur thing</t>
+          <t>Mohit Shrestha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7610,12 +8374,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -7625,99 +8389,367 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:21:53 AM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>01 Oct 2026 01:57:46 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>18h 8m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>4h 28m</t>
+          <t>18h 8m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>TKT1353546</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>som Bahadur thing</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:21:53 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>4h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>TKT1352969</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Naresh Acharya</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>30 Sep 2026 04:49:39 PM</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>21h 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1344823</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Saroj Man Shrestha</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:24:28 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:20:51 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:24:28 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>7d 1h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353539</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Chakra prasad thapa magar</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:13:51 AM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>5h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352583</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:15:03 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:49:09 PM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:22:49 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>23h 7m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6138,10 +6138,8 @@
           <t>bindu bhattrai</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9841881780</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9841881780</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6223,10 +6221,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6237,7 +6233,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6333,10 +6329,8 @@
           <t>Saroj Man Shrestha</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9843807409</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9843807409</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6371,10 +6365,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>27.67556</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>27.67556</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -6430,25 +6422,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.32319</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.32319</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6544,10 +6532,8 @@
           <t>Chakra prasad thapa magar</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9821507017</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9821507017</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6637,10 +6623,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6651,7 +6635,7 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6747,10 +6731,8 @@
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6785,10 +6767,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6844,25 +6824,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6911,7 +6887,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8585,7 +8561,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -8652,7 +8628,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -8719,7 +8695,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6867,6 +6867,412 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:01 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353679</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Lamichhane</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Lamichhane</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9849952080</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9849952080</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:38:04 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>loktanrik chowk Hile tole, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>04:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Subash Sunuwar</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>L30-4</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>4h 23m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:53 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>CONFINGURE ISSUE</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353468</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Bigyan Shrestha</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Bigyan Shrestha</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9746458564</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:18:34 AM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9813031745</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 07:30:42 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:53:21 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.68067</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Matatirtha Mahalaxmi school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>stha.bigyan03@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.23175</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>4h 34m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6878,7 +7284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6887,7 +7293,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6915,7 +7321,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6925,7 +7331,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -6936,7 +7342,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -6948,7 +7354,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 3m</t>
+          <t>3h 52m</t>
         </is>
       </c>
     </row>
@@ -6960,7 +7366,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 2m</t>
+          <t>1d 15h 17m</t>
         </is>
       </c>
     </row>
@@ -7001,14 +7407,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -7019,14 +7425,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -7127,14 +7533,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -7187,23 +7593,23 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7215,14 +7621,14 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -7233,12 +7639,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -7261,7 +7667,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -7284,187 +7690,143 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1352600</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Dhanishwar Subedi</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>30 Sep 2026 01:00:32 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>20h 14m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1352535</t>
+          <t>TKT1352600</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Bijay Tuladhar</t>
+          <t>Dhanishwar Subedi</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7494,22 +7856,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:20:00 PM</t>
+          <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -7519,29 +7881,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>21h 41m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1352779</t>
+          <t>TKT1352535</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Narayan kumar khatri</t>
+          <t>Bijay Tuladhar</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7561,22 +7923,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:58:48 PM</t>
+          <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -7586,7 +7948,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>21h 41m</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7990,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -7660,22 +8022,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1342441</t>
+          <t>TKT1352779</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Dex Nine pvt. Ltd.</t>
+          <t>Narayan kumar khatri</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7695,22 +8057,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 01:33:16 PM</t>
+          <t>30 Sep 2026 02:58:48 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7720,19 +8082,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>8d 21h 31m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1353606</t>
+          <t>TKT1342441</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7762,22 +8124,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:54:48 AM</t>
+          <t>22 Sep 2026 01:33:16 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7787,19 +8149,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>2h 9m</t>
+          <t>8d 21h 31m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1352339</t>
+          <t>TKT1353606</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Kamal Shali Ghimire</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7829,22 +8191,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 10:30:19 AM</t>
+          <t>01 Oct 2026 09:54:48 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -7854,29 +8216,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 48m</t>
+          <t>2h 9m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1348195</t>
+          <t>TKT1352339</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Anuj  Kuwar</t>
+          <t>Kamal Shali Ghimire</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7896,22 +8258,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 11:21:12 AM</t>
+          <t>30 Sep 2026 10:30:19 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -7921,39 +8283,39 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>4d 1h 5m</t>
+          <t>1d 1h 48m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1352921</t>
+          <t>TKT1348195</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Suresh Babu Amgain</t>
+          <t>Anuj  Kuwar</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -7963,32 +8325,32 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>27 Sep 2026 11:21:12 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:28:17 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>4d 1h 5m</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8424,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1351456</t>
+          <t>TKT1352921</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Puja Regmi</t>
+          <t>Suresh Babu Amgain</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8082,12 +8444,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -8097,44 +8459,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:48:59 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>01 Oct 2026 12:28:17 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 58m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 23h</t>
+          <t>19h 58m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1352734</t>
+          <t>TKT1351456</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Rupak Subedi</t>
+          <t>Puja Regmi</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -8164,22 +8526,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:34:05 PM</t>
+          <t>29 Sep 2026 01:48:59 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -8189,29 +8551,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>1d 23h</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1352510</t>
+          <t>TKT1352734</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Barjachrya</t>
+          <t>Rupak Subedi</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8231,22 +8593,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:05:06 PM</t>
+          <t>30 Sep 2026 02:34:05 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -8256,29 +8618,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 3m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1352942</t>
+          <t>TKT1352510</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Rajesh Barjachrya</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -8298,22 +8660,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:37:44 PM</t>
+          <t>30 Sep 2026 12:05:06 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -8323,39 +8685,39 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>20h 49m</t>
+          <t>1d 1h 3m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1353222</t>
+          <t>TKT1352942</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Mohit Shrestha</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -8365,44 +8727,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>30 Sep 2026 04:37:44 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:57:46 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>20h 49m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1353546</t>
+          <t>TKT1353222</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>som Bahadur thing</t>
+          <t>Mohit Shrestha</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8417,12 +8779,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -8432,54 +8794,54 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:21:53 AM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>01 Oct 2026 01:57:46 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>18h 8m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>4h 28m</t>
+          <t>18h 8m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1352969</t>
+          <t>TKT1353546</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Naresh Acharya</t>
+          <t>som Bahadur thing</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8499,22 +8861,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:58:17 PM</t>
+          <t>01 Oct 2026 01:50:39 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:49:39 PM</t>
+          <t>01 Oct 2026 09:21:53 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:58:17 PM</t>
+          <t>01 Oct 2026 01:50:39 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -8524,29 +8886,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>21h 8m</t>
+          <t>4h 28m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1344823</t>
+          <t>TKT1352969</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Saroj Man Shrestha</t>
+          <t>Naresh Acharya</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8566,22 +8928,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:24:28 PM</t>
+          <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>24 Sep 2026 01:20:51 PM</t>
+          <t>30 Sep 2026 04:49:39 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:24:28 PM</t>
+          <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -8591,19 +8953,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>7d 1h 3m</t>
+          <t>21h 8m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1353539</t>
+          <t>TKT1344823</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Chakra prasad thapa magar</t>
+          <t>Saroj Man Shrestha</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -8633,22 +8995,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:26:57 PM</t>
+          <t>01 Oct 2026 02:24:28 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:13:51 AM</t>
+          <t>24 Sep 2026 01:20:51 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:26:57 PM</t>
+          <t>01 Oct 2026 02:24:28 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -8658,74 +9020,208 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>5h 13m</t>
+          <t>7d 1h 3m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>TKT1353539</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Chakra prasad thapa magar</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:13:51 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>5h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>TKT1352583</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>30 Sep 2026 03:15:03 PM</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>30 Sep 2026 12:49:09 PM</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 02:22:49 PM</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>23h 7m</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>1d 1h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353679</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Susmita Lamichhane</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:38:04 AM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>4h 23m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -6924,20 +6924,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Susmita Lamichhane</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9849952080</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9849952080</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7023,10 +7017,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -7037,7 +7029,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7133,10 +7125,8 @@
           <t>Bigyan Shrestha</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9746458564</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9746458564</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7171,10 +7161,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.68067</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.68067</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7226,48 +7214,669 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB348</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.23175</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.23175000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>4h 34m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>4h 34m</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>7h 22m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:13 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346370</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9818548099</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:13:22 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9867369591</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:48:50 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:13:22 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.68548</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Madhya Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>anshusafalpatel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>00:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>CDB488</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.33084</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>5d 22h 24m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:03 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353556</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakurathi</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakurathi</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9841372017</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:03:29 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9805782711</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:27:16 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:03:30 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Suvakamana Gate, RadheRadhe Bhawan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>suren@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>05:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>5h 36m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353885</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bhandari</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bhandari</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9863635254</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9863635254</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:42:19 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.668862</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>3 Sundar Nagr Marg Balkot Bhaktapur Near By Rose Village., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>eramesh.bhandari@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>02:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L4-7</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.374149</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 20m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -7284,7 +7893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7321,7 +7930,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -7331,7 +7940,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -7342,7 +7951,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7963,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 52m</t>
+          <t>3h 23m</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7975,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 17m</t>
+          <t>1d 16h 39m</t>
         </is>
       </c>
     </row>
@@ -7407,14 +8016,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -7533,14 +8142,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -9191,14 +9800,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>Case : slow issue   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 03:01:53 PM</t>
@@ -9222,6 +9831,207 @@
       <c r="M51" s="5" t="inlineStr">
         <is>
           <t>4h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346370</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:13:22 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:48:50 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:13:22 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>5d 22h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353556</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Umesh Thakurathi</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:03:29 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:27:16 AM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:03:30 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>5h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353885</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bhandari</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:42:19 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>2h 20m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7324,10 +7324,8 @@
           <t>Kumari Nanda Jaiswar Bhatta</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9818548099</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9818548099</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7362,10 +7360,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.68548</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.68548</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -7421,25 +7417,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>CDB488</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.33084</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.33083999999999</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7535,10 +7527,8 @@
           <t>Umesh Thakurathi</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9841372017</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9841372017</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7628,10 +7618,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -7642,7 +7630,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7738,10 +7726,8 @@
           <t>Ramesh Bhandari</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9863635254</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9863635254</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7776,10 +7762,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.668862</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.668862</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7835,50 +7819,257 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L4-7</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.374149</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.374149</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 20m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>2h 20m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353585</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Sunaina Maharjan</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Sunaina Maharjan</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9862794549</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:45:05 AM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9880955162</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:45:05 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:30:54 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Balambu Gurjudhara, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>sunayanamah33@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>05:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB052</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -7893,7 +8084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7930,7 +8121,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7940,7 +8131,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -7951,7 +8142,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -7963,7 +8154,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 23m</t>
+          <t>3h 28m</t>
         </is>
       </c>
     </row>
@@ -7975,7 +8166,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 39m</t>
+          <t>1d 15h 15m</t>
         </is>
       </c>
     </row>
@@ -8016,14 +8207,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8142,14 +8333,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9867,7 +10058,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -9934,7 +10125,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -10001,14 +10192,14 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 03:02:38 PM</t>
@@ -10032,6 +10223,73 @@
       <c r="M54" s="3" t="inlineStr">
         <is>
           <t>2h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353585</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Sunaina Maharjan</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:45:05 AM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:45:05 AM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:30:54 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -7929,10 +7929,8 @@
           <t>Sunaina Maharjan</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9862794549</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9862794549</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7967,10 +7965,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8026,50 +8022,257 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB052</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>5h 45m</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>5h 45m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:43 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>secondary router connection</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352458</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Mohsin Ansari</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Mohsin Ansari</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9849565480</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:43:31 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849565489</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:31:10 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:43:31 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>27.69766201137519, 85.30675643311395 GPS Coordinates Nearest: KAT008-01-2/11-ADB005 (0m Road) Map: C</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>amohsin20@britishmodelcollege.edu.np</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>14:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>CDB327</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8121,7 +8324,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -8131,7 +8334,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -8142,7 +8345,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8357,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 28m</t>
+          <t>3h 20m</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8369,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 15m</t>
+          <t>1d 14h 49m</t>
         </is>
       </c>
     </row>
@@ -8207,14 +8410,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -8329,41 +8532,41 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8375,18 +8578,18 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8601,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -8416,23 +8619,23 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8444,14 +8647,14 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -8462,12 +8665,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -8490,7 +8693,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -8513,187 +8716,143 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1352600</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Dhanishwar Subedi</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>30 Sep 2026 01:00:32 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>20h 14m</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1352535</t>
+          <t>TKT1352600</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Bijay Tuladhar</t>
+          <t>Dhanishwar Subedi</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -8723,22 +8882,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:20:00 PM</t>
+          <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -8748,29 +8907,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>21h 41m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1352779</t>
+          <t>TKT1352535</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Narayan kumar khatri</t>
+          <t>Bijay Tuladhar</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -8790,22 +8949,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:58:48 PM</t>
+          <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -8815,7 +8974,7 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>21h 41m</t>
         </is>
       </c>
     </row>
@@ -8857,7 +9016,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -8889,22 +9048,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1342441</t>
+          <t>TKT1352779</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Dex Nine pvt. Ltd.</t>
+          <t>Narayan kumar khatri</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -8924,22 +9083,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 01:33:16 PM</t>
+          <t>30 Sep 2026 02:58:48 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -8949,19 +9108,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>8d 21h 31m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1353606</t>
+          <t>TKT1342441</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -8991,22 +9150,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:54:48 AM</t>
+          <t>22 Sep 2026 01:33:16 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -9016,19 +9175,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2h 9m</t>
+          <t>8d 21h 31m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1352339</t>
+          <t>TKT1353606</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Kamal Shali Ghimire</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -9058,22 +9217,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 10:30:19 AM</t>
+          <t>01 Oct 2026 09:54:48 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -9083,29 +9242,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 48m</t>
+          <t>2h 9m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1348195</t>
+          <t>TKT1352339</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Anuj  Kuwar</t>
+          <t>Kamal Shali Ghimire</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -9125,22 +9284,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 11:21:12 AM</t>
+          <t>30 Sep 2026 10:30:19 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -9150,39 +9309,39 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 5m</t>
+          <t>1d 1h 48m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1352921</t>
+          <t>TKT1348195</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Suresh Babu Amgain</t>
+          <t>Anuj  Kuwar</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -9192,32 +9351,32 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>27 Sep 2026 11:21:12 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:28:17 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>4d 1h 5m</t>
         </is>
       </c>
     </row>
@@ -9291,12 +9450,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1351456</t>
+          <t>TKT1352921</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Puja Regmi</t>
+          <t>Suresh Babu Amgain</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -9311,12 +9470,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -9326,44 +9485,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:48:59 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>01 Oct 2026 12:28:17 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 58m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 23h</t>
+          <t>19h 58m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1352734</t>
+          <t>TKT1351456</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Rupak Subedi</t>
+          <t>Puja Regmi</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9393,22 +9552,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:34:05 PM</t>
+          <t>29 Sep 2026 01:48:59 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -9418,29 +9577,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>1d 23h</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1352510</t>
+          <t>TKT1352734</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Rajesh Barjachrya</t>
+          <t>Rupak Subedi</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -9460,22 +9619,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:05:06 PM</t>
+          <t>30 Sep 2026 02:34:05 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -9485,29 +9644,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 3m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1352942</t>
+          <t>TKT1352510</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Rajesh Barjachrya</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -9527,22 +9686,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:37:44 PM</t>
+          <t>30 Sep 2026 12:05:06 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -9552,39 +9711,39 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>20h 49m</t>
+          <t>1d 1h 3m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1353222</t>
+          <t>TKT1352942</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Mohit Shrestha</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -9594,44 +9753,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>30 Sep 2026 04:37:44 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:57:46 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>20h 49m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1353546</t>
+          <t>TKT1353222</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>som Bahadur thing</t>
+          <t>Mohit Shrestha</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -9646,12 +9805,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -9661,54 +9820,54 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:21:53 AM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>01 Oct 2026 01:57:46 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>18h 8m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>4h 28m</t>
+          <t>18h 8m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1352969</t>
+          <t>TKT1353546</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Naresh Acharya</t>
+          <t>som Bahadur thing</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -9728,22 +9887,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:58:17 PM</t>
+          <t>01 Oct 2026 01:50:39 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:49:39 PM</t>
+          <t>01 Oct 2026 09:21:53 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:58:17 PM</t>
+          <t>01 Oct 2026 01:50:39 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -9753,29 +9912,29 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>21h 8m</t>
+          <t>4h 28m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1344823</t>
+          <t>TKT1352969</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Saroj Man Shrestha</t>
+          <t>Naresh Acharya</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -9795,22 +9954,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:24:28 PM</t>
+          <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>24 Sep 2026 01:20:51 PM</t>
+          <t>30 Sep 2026 04:49:39 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:24:28 PM</t>
+          <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -9820,19 +9979,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>7d 1h 3m</t>
+          <t>21h 8m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1353539</t>
+          <t>TKT1344823</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Chakra prasad thapa magar</t>
+          <t>Saroj Man Shrestha</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -9862,22 +10021,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:26:57 PM</t>
+          <t>01 Oct 2026 02:24:28 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:13:51 AM</t>
+          <t>24 Sep 2026 01:20:51 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:26:57 PM</t>
+          <t>01 Oct 2026 02:24:28 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -9887,39 +10046,39 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>5h 13m</t>
+          <t>7d 1h 3m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1352583</t>
+          <t>TKT1353539</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Chakra prasad thapa magar</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -9929,64 +10088,64 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 03:15:03 PM</t>
+          <t>01 Oct 2026 02:26:57 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:49:09 PM</t>
+          <t>01 Oct 2026 09:13:51 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:22:49 PM</t>
+          <t>01 Oct 2026 02:26:57 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>23h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 33m</t>
+          <t>5h 13m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1353679</t>
+          <t>TKT1352583</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Susmita Lamichhane</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -9996,44 +10155,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:01:53 PM</t>
+          <t>30 Sep 2026 03:15:03 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:38:04 AM</t>
+          <t>30 Sep 2026 12:49:09 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:01:53 PM</t>
+          <t>01 Oct 2026 02:22:49 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 7m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>4h 23m</t>
+          <t>1d 1h 33m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1346370</t>
+          <t>TKT1353679</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Kumari Nanda Jaiswar Bhatta</t>
+          <t>Susmita Lamichhane</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -10063,22 +10222,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:13:22 PM</t>
+          <t>01 Oct 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>25 Sep 2026 04:48:50 PM</t>
+          <t>01 Oct 2026 10:38:04 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:13:22 PM</t>
+          <t>01 Oct 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -10088,19 +10247,19 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>5d 22h 24m</t>
+          <t>4h 23m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1353556</t>
+          <t>TKT1346370</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Umesh Thakurathi</t>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -10130,22 +10289,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:03:29 PM</t>
+          <t>01 Oct 2026 03:13:22 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:27:16 AM</t>
+          <t>25 Sep 2026 04:48:50 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:03:30 PM</t>
+          <t>01 Oct 2026 03:13:22 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -10155,19 +10314,19 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>5h 36m</t>
+          <t>5d 22h 24m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1353885</t>
+          <t>TKT1353556</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Ramesh Bhandari</t>
+          <t>Umesh Thakurathi</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -10197,22 +10356,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:02:38 PM</t>
+          <t>01 Oct 2026 03:03:29 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:42:19 PM</t>
+          <t>01 Oct 2026 09:27:16 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:02:38 PM</t>
+          <t>01 Oct 2026 03:03:30 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -10222,74 +10381,208 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>2h 20m</t>
+          <t>5h 36m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>TKT1353885</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Ramesh Bhandari</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:42:19 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>2h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
           <t>TKT1353585</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Sunaina Maharjan</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:45:05 AM</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 09:45:05 AM</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 03:30:54 PM</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>5h 45m</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr">
         <is>
           <t>5h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352458</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Mohsin Ansari</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:43:31 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:31:10 AM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:43:31 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8132,10 +8132,8 @@
           <t>Mohsin Ansari</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9849565480</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9849565480</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8170,10 +8168,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -8229,50 +8225,464 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>CDB327</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:53 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353930</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Rekha Rana</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Rekha Rana</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9815651617</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:53:28 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9851651617</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:09:35 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:53:28 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.694877</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Near  to Milan Chowk,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>ranarekha504@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>02:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L30-3</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.342056</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 12m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2h 43m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW39" s="3" t="inlineStr">
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:55 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353055</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9708478044</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:55:19 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9849426510</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:41 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:55:19 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.682799</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Holy garden school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>08:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L38-7</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.389388</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8324,7 +8734,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -8334,7 +8744,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -8345,7 +8755,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8767,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 20m</t>
+          <t>3h 6m</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8779,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 49m</t>
+          <t>1d 12h 57m</t>
         </is>
       </c>
     </row>
@@ -8410,14 +8820,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -8559,14 +8969,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -10552,14 +10962,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 03:43:31 PM</t>
@@ -10583,6 +10993,140 @@
       <c r="M57" s="5" t="inlineStr">
         <is>
           <t>1d 4h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353930</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Rekha Rana</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:53:28 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:09:35 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:53:28 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>2h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353055</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:55:19 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:41 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:55:19 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW41"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8335,10 +8335,8 @@
           <t>Rekha Rana</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9815651617</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9815651617</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8373,10 +8371,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.694877</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.694877</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -8432,25 +8428,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>L30-3</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.342056</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.342056</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8546,10 +8538,8 @@
           <t>BISHNU HARI SHRESTHA</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9708478044</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9708478044</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8584,10 +8574,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.682799</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.682799</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8639,50 +8627,257 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>L38-7</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.389388</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.389388</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:06 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>6G router setup request</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353605</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Adhikari</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Adhikari</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9860589232</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9860589232</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:54:39 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.744763</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Model School, à¤¶à¥à¤°à¥€à¤Ÿà¥‹à¤², Tokha 44600, 27.74397, 85.33182, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>a.saroj463@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>06:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr"/>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L2-3</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.335609</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>22h 22m</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV41" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW41" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8734,7 +8929,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -8744,7 +8939,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -8755,7 +8950,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8962,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 6m</t>
+          <t>2h 59m</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8974,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 57m</t>
+          <t>1d 11h 53m</t>
         </is>
       </c>
     </row>
@@ -8820,14 +9015,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -8969,14 +9164,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11224,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -11096,14 +11291,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>01 Oct 2026 03:55:19 PM</t>
@@ -11127,6 +11322,73 @@
       <c r="M59" s="5" t="inlineStr">
         <is>
           <t>22h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353605</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Adhikari</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:54:39 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW42"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -8737,10 +8737,8 @@
           <t>Saroj Adhikari</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9860589232</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9860589232</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8775,10 +8773,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.744763</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.744763</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8834,50 +8830,253 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L2-3</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.335609</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.33560900000001</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
           <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV  SETBOX ISSUE</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353893</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Gita bhujel</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Gita bhujel</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9808751233</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:19:05 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9808751233</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:47:20 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:19:05 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.746223</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>dhapasi height, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>03:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L4-4</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.330001</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>6h 11m</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>3h 31m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV42" s="3" t="inlineStr">
-        <is>
-          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW42" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -8892,7 +9091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8929,7 +9128,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -8939,7 +9138,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -8950,7 +9149,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -8962,7 +9161,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 59m</t>
+          <t>2h 53m</t>
         </is>
       </c>
     </row>
@@ -8974,7 +9173,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 11h 53m</t>
+          <t>1d 10h 48m</t>
         </is>
       </c>
     </row>
@@ -9033,14 +9232,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -9187,14 +9386,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -11358,14 +11557,14 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
           <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 04:06:04 PM</t>
@@ -11389,6 +11588,73 @@
       <c r="M60" s="3" t="inlineStr">
         <is>
           <t>6h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353893</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Gita bhujel</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:19:05 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:47:20 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:19:05 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>3h 31m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -8940,10 +8940,8 @@
           <t>Gita bhujel</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9808751233</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9808751233</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8978,10 +8976,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.746223</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.746223</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9033,50 +9029,1312 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L4-4</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.330001</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.330001</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>3h 31m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:36 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353808</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>dorje lama</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>dorje lama</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9849177135</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:36:50 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>BKT9849177135</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:48:04 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:36:50 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>kamalbinayak , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>bdc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>04:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>L57-6</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>3h 31m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4h 48m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:37 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353582</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:37:22 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.68641</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri Municipality Ward No. 6 Office Details from Google Maps M6QG+77W, Chandragiri 44600, Ba</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>saphaltmang555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>06:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB365</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.226968</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:36 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353582</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:37:22 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.68641</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri Municipality Ward No. 6 Office Details from Google Maps M6QG+77W, Chandragiri 44600, Ba</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>saphaltmang555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>06:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>CDB365</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.226968</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:32 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353091</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:32:01 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.68618</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Balkhu Opposite of BPA college, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>vision.ghimire96@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>08:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>CDB164</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.29338</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:31 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353091</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:32:01 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.68618</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Balkhu Opposite of BPA college, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>vision.ghimire96@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>08:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB164</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.29338</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:30 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350037</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>S K Mustafa</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>S K Mustafa</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9818066040</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9818066040</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:30:42 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.707037</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Nera Jagat Sundar Bwonekuthi Secondary School,P842+XPF, ????????? ?????? ???, Kathmandu 44600, Bagma</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>ali.sksabir@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>08:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.301797</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 32m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 32m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -9091,7 +10349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9128,7 +10386,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -9138,7 +10396,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -9149,7 +10407,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9161,7 +10419,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 53m</t>
+          <t>6h 6m</t>
         </is>
       </c>
     </row>
@@ -9173,7 +10431,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 10h 48m</t>
+          <t>1d 8h 50m</t>
         </is>
       </c>
     </row>
@@ -9214,14 +10472,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -9250,10 +10508,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -9363,14 +10621,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -9474,7 +10732,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -9492,12 +10750,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -9520,7 +10778,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -9543,187 +10801,143 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1352600</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Dhanishwar Subedi</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>30 Sep 2026 01:00:32 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>01 Oct 2026 09:15:18 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>20h 14m</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1352535</t>
+          <t>TKT1352600</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Bijay Tuladhar</t>
+          <t>Dhanishwar Subedi</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -9753,22 +10967,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:20:00 PM</t>
+          <t>30 Sep 2026 01:00:32 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:01:43 AM</t>
+          <t>01 Oct 2026 09:15:18 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -9778,29 +10992,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>21h 41m</t>
+          <t>20h 14m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1352779</t>
+          <t>TKT1352535</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Narayan kumar khatri</t>
+          <t>Bijay Tuladhar</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -9820,22 +11034,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:58:48 PM</t>
+          <t>30 Sep 2026 12:20:00 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:42:05 AM</t>
+          <t>01 Oct 2026 10:01:43 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -9845,7 +11059,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>21h 41m</t>
         </is>
       </c>
     </row>
@@ -9887,7 +11101,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -9919,22 +11133,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1342441</t>
+          <t>TKT1352779</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Dex Nine pvt. Ltd.</t>
+          <t>Narayan kumar khatri</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -9954,22 +11168,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 01:33:16 PM</t>
+          <t>30 Sep 2026 02:58:48 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 11:04:18 AM</t>
+          <t>01 Oct 2026 11:42:05 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -9979,19 +11193,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>8d 21h 31m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1353606</t>
+          <t>TKT1342441</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Sudip Shrestha</t>
+          <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -10021,22 +11235,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:54:48 AM</t>
+          <t>22 Sep 2026 01:33:16 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:04:05 PM</t>
+          <t>01 Oct 2026 11:04:18 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -10046,19 +11260,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2h 9m</t>
+          <t>8d 21h 31m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1352339</t>
+          <t>TKT1353606</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Kamal Shali Ghimire</t>
+          <t>Sudip Shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -10088,22 +11302,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 10:30:19 AM</t>
+          <t>01 Oct 2026 09:54:48 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:19:17 PM</t>
+          <t>01 Oct 2026 12:04:05 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -10113,29 +11327,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 48m</t>
+          <t>2h 9m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1348195</t>
+          <t>TKT1352339</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Anuj  Kuwar</t>
+          <t>Kamal Shali Ghimire</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10155,22 +11369,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 11:21:12 AM</t>
+          <t>30 Sep 2026 10:30:19 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:26:25 PM</t>
+          <t>01 Oct 2026 12:19:17 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -10180,39 +11394,39 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>4d 1h 5m</t>
+          <t>1d 1h 48m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1352921</t>
+          <t>TKT1348195</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Suresh Babu Amgain</t>
+          <t>Anuj  Kuwar</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -10222,32 +11436,32 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:29:35 PM</t>
+          <t>27 Sep 2026 11:21:12 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:28:17 PM</t>
+          <t>01 Oct 2026 12:26:25 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>19h 58m</t>
+          <t>4d 1h 5m</t>
         </is>
       </c>
     </row>
@@ -10321,12 +11535,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1351456</t>
+          <t>TKT1352921</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Puja Regmi</t>
+          <t>Suresh Babu Amgain</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -10341,12 +11555,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -10356,44 +11570,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:48:59 PM</t>
+          <t>30 Sep 2026 04:29:35 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:49:05 PM</t>
+          <t>01 Oct 2026 12:28:17 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>19h 58m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 23h</t>
+          <t>19h 58m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1352734</t>
+          <t>TKT1351456</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Rupak Subedi</t>
+          <t>Puja Regmi</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -10423,22 +11637,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 02:34:05 PM</t>
+          <t>29 Sep 2026 01:48:59 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:02:33 PM</t>
+          <t>01 Oct 2026 12:49:05 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -10448,29 +11662,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>1d 23h</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1352510</t>
+          <t>TKT1352734</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Barjachrya</t>
+          <t>Rupak Subedi</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -10490,22 +11704,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:05:06 PM</t>
+          <t>30 Sep 2026 02:34:05 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:08:32 PM</t>
+          <t>01 Oct 2026 01:02:33 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -10515,29 +11729,29 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 3m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1352942</t>
+          <t>TKT1352510</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Rajesh Barjachrya</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -10557,22 +11771,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:37:44 PM</t>
+          <t>30 Sep 2026 12:05:06 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:27:30 PM</t>
+          <t>01 Oct 2026 01:08:32 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -10582,39 +11796,39 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>20h 49m</t>
+          <t>1d 1h 3m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1353222</t>
+          <t>TKT1352942</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Mohit Shrestha</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -10624,44 +11838,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 07:48:59 PM</t>
+          <t>30 Sep 2026 04:37:44 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:57:46 PM</t>
+          <t>01 Oct 2026 01:27:30 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>18h 8m</t>
+          <t>20h 49m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1353546</t>
+          <t>TKT1353222</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>som Bahadur thing</t>
+          <t>Mohit Shrestha</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -10676,12 +11890,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -10691,54 +11905,54 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:21:53 AM</t>
+          <t>30 Sep 2026 07:48:59 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:50:39 PM</t>
+          <t>01 Oct 2026 01:57:46 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>18h 8m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>4h 28m</t>
+          <t>18h 8m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1352969</t>
+          <t>TKT1353546</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Naresh Acharya</t>
+          <t>som Bahadur thing</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -10758,22 +11972,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:58:17 PM</t>
+          <t>01 Oct 2026 01:50:39 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>30 Sep 2026 04:49:39 PM</t>
+          <t>01 Oct 2026 09:21:53 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:58:17 PM</t>
+          <t>01 Oct 2026 01:50:39 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -10783,29 +11997,29 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>21h 8m</t>
+          <t>4h 28m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1344823</t>
+          <t>TKT1352969</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Saroj Man Shrestha</t>
+          <t>Naresh Acharya</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -10825,22 +12039,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:24:28 PM</t>
+          <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>24 Sep 2026 01:20:51 PM</t>
+          <t>30 Sep 2026 04:49:39 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:24:28 PM</t>
+          <t>01 Oct 2026 01:58:17 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -10850,19 +12064,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>7d 1h 3m</t>
+          <t>21h 8m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1353539</t>
+          <t>TKT1344823</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Chakra prasad thapa magar</t>
+          <t>Saroj Man Shrestha</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10892,22 +12106,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:26:57 PM</t>
+          <t>01 Oct 2026 02:24:28 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:13:51 AM</t>
+          <t>24 Sep 2026 01:20:51 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:26:57 PM</t>
+          <t>01 Oct 2026 02:24:28 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -10917,39 +12131,39 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>5h 13m</t>
+          <t>7d 1h 3m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1352583</t>
+          <t>TKT1353539</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Chakra prasad thapa magar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -10959,64 +12173,64 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 03:15:03 PM</t>
+          <t>01 Oct 2026 02:26:57 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 12:49:09 PM</t>
+          <t>01 Oct 2026 09:13:51 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 02:22:49 PM</t>
+          <t>01 Oct 2026 02:26:57 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>23h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 33m</t>
+          <t>5h 13m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1353679</t>
+          <t>TKT1352583</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Susmita Lamichhane</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -11026,44 +12240,44 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:01:53 PM</t>
+          <t>30 Sep 2026 03:15:03 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 10:38:04 AM</t>
+          <t>30 Sep 2026 12:49:09 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:01:53 PM</t>
+          <t>01 Oct 2026 02:22:49 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 7m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>4h 23m</t>
+          <t>1d 1h 33m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1346370</t>
+          <t>TKT1353679</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Kumari Nanda Jaiswar Bhatta</t>
+          <t>Susmita Lamichhane</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -11093,22 +12307,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:13:22 PM</t>
+          <t>01 Oct 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>25 Sep 2026 04:48:50 PM</t>
+          <t>01 Oct 2026 10:38:04 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:13:22 PM</t>
+          <t>01 Oct 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -11118,19 +12332,19 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>5d 22h 24m</t>
+          <t>4h 23m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1353556</t>
+          <t>TKT1346370</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Umesh Thakurathi</t>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -11160,22 +12374,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:03:29 PM</t>
+          <t>01 Oct 2026 03:13:22 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:27:16 AM</t>
+          <t>25 Sep 2026 04:48:50 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:03:30 PM</t>
+          <t>01 Oct 2026 03:13:22 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -11185,19 +12399,19 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>5h 36m</t>
+          <t>5d 22h 24m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1353885</t>
+          <t>TKT1353556</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Ramesh Bhandari</t>
+          <t>Umesh Thakurathi</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -11227,22 +12441,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:02:38 PM</t>
+          <t>01 Oct 2026 03:03:29 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 12:42:19 PM</t>
+          <t>01 Oct 2026 09:27:16 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:02:38 PM</t>
+          <t>01 Oct 2026 03:03:30 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -11252,19 +12466,19 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2h 20m</t>
+          <t>5h 36m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1353585</t>
+          <t>TKT1353885</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Sunaina Maharjan</t>
+          <t>Ramesh Bhandari</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -11279,12 +12493,12 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -11294,44 +12508,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:45:05 AM</t>
+          <t>01 Oct 2026 03:02:38 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:45:05 AM</t>
+          <t>01 Oct 2026 12:42:19 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:30:54 PM</t>
+          <t>01 Oct 2026 03:02:38 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>5h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>5h 45m</t>
+          <t>2h 20m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1352458</t>
+          <t>TKT1353585</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Mohsin Ansari</t>
+          <t>Sunaina Maharjan</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -11341,17 +12555,17 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -11361,44 +12575,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:43:31 PM</t>
+          <t>01 Oct 2026 09:45:05 AM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 11:31:10 AM</t>
+          <t>01 Oct 2026 09:45:05 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:43:31 PM</t>
+          <t>01 Oct 2026 03:30:54 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 45m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 12m</t>
+          <t>5h 45m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1353930</t>
+          <t>TKT1352458</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Rekha Rana</t>
+          <t>Mohsin Ansari</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -11408,7 +12622,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -11428,22 +12642,22 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:53:28 PM</t>
+          <t>01 Oct 2026 03:43:31 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:09:35 PM</t>
+          <t>30 Sep 2026 11:31:10 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:53:28 PM</t>
+          <t>01 Oct 2026 03:43:31 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -11453,19 +12667,19 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>2h 43m</t>
+          <t>1d 4h 12m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1353055</t>
+          <t>TKT1353930</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>BISHNU HARI SHRESTHA</t>
+          <t>Rekha Rana</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -11495,22 +12709,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:55:19 PM</t>
+          <t>01 Oct 2026 03:53:28 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>30 Sep 2026 05:32:41 PM</t>
+          <t>01 Oct 2026 01:09:35 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 03:55:19 PM</t>
+          <t>01 Oct 2026 03:53:28 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -11520,19 +12734,19 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>2h 43m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1353605</t>
+          <t>TKT1353055</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Saroj Adhikari</t>
+          <t>BISHNU HARI SHRESTHA</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -11562,22 +12776,22 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 04:06:04 PM</t>
+          <t>01 Oct 2026 03:55:19 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:54:39 AM</t>
+          <t>30 Sep 2026 05:32:41 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 04:06:04 PM</t>
+          <t>01 Oct 2026 03:55:19 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -11587,74 +12801,543 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>6h 11m</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
+          <t>TKT1353605</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Saroj Adhikari</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:54:39 AM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
           <t>TKT1353893</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Gita bhujel</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 04:19:05 PM</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 12:47:20 PM</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 04:19:05 PM</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="M62" s="3" t="inlineStr">
         <is>
           <t>3h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353808</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>dorje lama</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:36:50 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:48:04 AM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:36:50 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>4h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353582</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:37:22 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353582</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:37:22 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353091</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:32:01 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353091</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:32:01 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350037</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>S K Mustafa</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:30:42 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 32m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9129,20 +9129,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>dorje lama</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9849177135</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9849177135</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9177,10 +9171,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9236,25 +9228,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>L57-6</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9350,10 +9338,8 @@
           <t>Sapana Tamang</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9840008359</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9840008359</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9388,10 +9374,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.68641</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.68641</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9447,25 +9431,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>CDB365</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.226968</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.226968</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9561,10 +9541,8 @@
           <t>Sapana Tamang</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9840008359</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9840008359</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9599,10 +9577,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.68641</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.68641</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9658,25 +9634,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>CDB365</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.226968</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.226968</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9772,10 +9744,8 @@
           <t>Alternative Herbal Products Pvt Ltd</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9849215450</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9849215450</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9810,10 +9780,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.68618</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.68618</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9869,25 +9837,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>CDB164</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.29338</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.29338</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9983,10 +9947,8 @@
           <t>Alternative Herbal Products Pvt Ltd</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9849215450</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9849215450</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10021,10 +9983,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.68618</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.68618</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -10080,25 +10040,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>CDB164</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.29338</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.29338</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -10194,10 +10150,8 @@
           <t>S K Mustafa</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9818066040</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9818066040</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10232,10 +10186,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.707037</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.707037</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -10291,25 +10243,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.301797</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.30179699999999</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10358,7 +10306,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12972,7 +12920,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -13039,7 +12987,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -13106,7 +13054,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -13173,7 +13121,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -13240,7 +13188,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -13307,7 +13255,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW49"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10286,6 +10286,428 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:03 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352766</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841304879</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9880756943</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.71567</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Behind Bishnu Bimala Kunja, Near Nagarkot dairy- Naya Basti-  Kumarigal Boudha- 6, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>sonicnapit0104@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>12:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.36795</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:02 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352766</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9841304879</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9880756943</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.71567</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Behind Bishnu Bimala Kunja, Near Nagarkot dairy- Naya Basti-  Kumarigal Boudha- 6, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>sonicnapit0104@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>12:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.36795</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10297,7 +10719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10306,7 +10728,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10334,7 +10756,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -10344,7 +10766,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -10355,7 +10777,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10789,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 6m</t>
+          <t>5h 47m</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10801,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 8h 50m</t>
+          <t>1d 8h 29m</t>
         </is>
       </c>
     </row>
@@ -10420,14 +10842,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -10569,14 +10991,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -13289,6 +13711,140 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352766</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352766</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW51"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10353,10 +10353,8 @@
           <t>Sonic Napit</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841304879</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841304879</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10391,10 +10389,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.71567</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.71567</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10450,25 +10446,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.36795</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.36794999999999</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10564,10 +10556,8 @@
           <t>Sonic Napit</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9841304879</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9841304879</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10602,10 +10592,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.71567</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.71567</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10661,50 +10649,249 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.36795</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.36794999999999</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 12m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:25 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352880</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9867339967</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:04:27 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>KLK9867339967</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:04:27 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:25:36 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr"/>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Kirtipur Hospital, Kirtipur Ring Rd, Kathmandu 44618, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>apyfx.np@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>11:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>CDB191</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr"/>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10756,7 +10943,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -10766,7 +10953,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -10777,7 +10964,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -10789,7 +10976,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 47m</t>
+          <t>6h 17m</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10988,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 8h 29m</t>
+          <t>1d 8h 18m</t>
         </is>
       </c>
     </row>
@@ -10842,14 +11029,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -10991,14 +11178,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -13744,7 +13931,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -13811,14 +13998,14 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 05:03:23 PM</t>
@@ -13842,6 +14029,73 @@
       <c r="M70" s="3" t="inlineStr">
         <is>
           <t>1d 2h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1352880</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:04:27 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:04:27 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:25:36 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW52"/>
+  <dimension ref="A1:AW54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10759,10 +10759,8 @@
           <t>Anil Pandey</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9867339967</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9867339967</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10852,10 +10850,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
@@ -10866,30 +10862,436 @@
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 21m</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 21m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:37 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>worst internet service</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350654</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9700971170</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 09:53:45 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9823190890R</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:40:24 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:37:27 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.66368,</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>ala Futsal &amp; Recreational Center Details from Google Maps Unnamed Road, M87P+5VQ, ?????????? 44700 +</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>rs1460451@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr"/>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr"/>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.33794</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>19h 43m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 57m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:35 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353804</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:35:45 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:46:37 AM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:35:45 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>balkot, shanti chock, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>05:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L53-8</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>5h 49m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -10906,7 +11308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10943,7 +11345,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -10953,7 +11355,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -10964,7 +11366,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -10976,7 +11378,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 17m</t>
+          <t>6h 8m</t>
         </is>
       </c>
     </row>
@@ -10988,7 +11390,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 8h 18m</t>
+          <t>1d 7h 39m</t>
         </is>
       </c>
     </row>
@@ -11029,14 +11431,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -11083,14 +11485,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -11178,14 +11580,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -11385,14 +11787,14 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -14065,14 +14467,14 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>30 Sep 2026 04:04:27 PM</t>
@@ -14096,6 +14498,73 @@
       <c r="M71" s="5" t="inlineStr">
         <is>
           <t>1d 1h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353804</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:35:45 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:46:37 AM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:35:45 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>5h 49m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW54"/>
+  <dimension ref="A1:AW55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10958,10 +10958,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11051,25 +11049,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -11165,10 +11159,8 @@
           <t>bindu bhattrai</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9841881780</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9841881780</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11254,10 +11246,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -11268,30 +11258,233 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>5h 49m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS54" s="3" t="inlineStr">
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:56 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354116</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Rabin Thapa</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Rabin Thapa</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9808069533</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:56:20 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9808069533</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:54:01 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:56:20 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Nayabasti youth club, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>rabinthapa422@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>02:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>L24-8</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
-          <t>5h 49m</t>
-        </is>
-      </c>
-      <c r="AU54" s="3" t="inlineStr">
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>2h 2m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV54" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW54" s="3" t="inlineStr">
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -11308,7 +11501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11345,7 +11538,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -11355,7 +11548,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -11366,7 +11559,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11571,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 8m</t>
+          <t>5h 59m</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11583,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 7h 39m</t>
+          <t>1d 6h 55m</t>
         </is>
       </c>
     </row>
@@ -11431,14 +11624,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -11580,14 +11773,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -14534,14 +14727,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
           <t>01 Oct 2026 05:35:45 PM</t>
@@ -14565,6 +14758,73 @@
       <c r="M72" s="3" t="inlineStr">
         <is>
           <t>5h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1354116</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Rabin Thapa</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:56:20 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:54:01 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:56:20 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>2h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_01_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_01_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11354,10 +11354,8 @@
           <t>Rabin Thapa</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9808069533</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9808069533</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11447,10 +11445,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
@@ -11461,7 +11457,7 @@
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11510,7 +11506,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14794,7 +14790,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
